--- a/pages/shp/uploads/26-09-2025 - 26-09-2025.xlsx
+++ b/pages/shp/uploads/26-09-2025 - 26-09-2025.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="328">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -339,34 +339,121 @@
     <t>KODE JENIS PENGANGKUTAN</t>
   </si>
   <si>
-    <t>00026174540620250926000396</t>
-  </si>
-  <si>
-    <t>261</t>
+    <t>00003074540620250926001448</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>050100</t>
   </si>
   <si>
     <t>050500</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>ITMIL</t>
+  </si>
+  <si>
+    <t>IDCGK</t>
+  </si>
+  <si>
+    <t>TWTPE</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>2025-09-26</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
+    <t>DN</t>
+  </si>
+  <si>
     <t>BANDUNG</t>
   </si>
   <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
     <t>YUS YULIUS</t>
   </si>
   <si>
-    <t>EXIM MANAGER</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>021150</t>
+    <t>MANAGER EXIM</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>468733</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>00003074540620250926001447</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>087346</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>02450000</t>
+  </si>
+  <si>
+    <t>VNSGN</t>
+  </si>
+  <si>
+    <t>468558</t>
+  </si>
+  <si>
+    <t>00003074540620250926001446</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>AEDXB</t>
+  </si>
+  <si>
+    <t>467222</t>
+  </si>
+  <si>
+    <t>00003074540620250926001449</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>USELA</t>
+  </si>
+  <si>
+    <t>468602</t>
   </si>
   <si>
     <t>KODE FASILITAS TARIF</t>
@@ -381,148 +468,168 @@
     <t>NPWP BILLING</t>
   </si>
   <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>PT NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL. RAYA RANCAEKEK MAJALAYA NO. 289 001/007 SOLOKANJERUK, SOLOKANJERUK, BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>JL. RAYA RANCAEKEK MAJALAYA NO. 289 RT. 001
+RW. 007 001/007 SOLOKANJERUK,
+SOLOKANJERUK, BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>0029142445012000000000</t>
+  </si>
+  <si>
+    <t>FEDEX EXPRESS INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>GEDUNG SOUTH QUARTER LT 12 TOWER C JL RADEN AJENG KARTINI KAV 8 RT.010 RW.004, CILANDAK BARAT, CILANDAK, KOTA ADMINISTRASI JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>GREAT GIANT FIBER GARMENT CO., LTD.</t>
+  </si>
+  <si>
+    <t>5F., NO.73. FU HSING N.ROAD, 10503 TAIPEI CITY
+ATTN : VITA HSIAO#219 &amp; REBECCA</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>PPH</t>
-  </si>
-  <si>
-    <t>PPN</t>
-  </si>
-  <si>
-    <t>BMTP</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
-  </si>
-  <si>
-    <t>NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289   SOLOKANJERUK SOLOKANJERUK KAB. BANDUNG JAWA BARAT</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 SOLOKANJERUK SOLOKANJERUK KAB. BANDUNG JAWA BARAT</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
+    <t>0013107743062000000000</t>
+  </si>
+  <si>
+    <t>BIROTIKA SEMESTA</t>
+  </si>
+  <si>
+    <t>MULIA BUSINESS PARK BLD F, JL MT.
+HARYONO KAV 58-60, PANCORAN, PANCORAN,
+KOTA ADM. JAKARTA SELATAN, DKI JAKARTA,
+53201</t>
+  </si>
+  <si>
+    <t>CHUTEX INTERNATIONAL CO., LTD</t>
+  </si>
+  <si>
+    <t>18, THONG NHAT ROAD
+SONG THAN 2 INDUSTRIAL ZONE
+DI AN TOWN WARD, HO CHI MINH CITY
+BINH DUONG BINH DUONG
+VIETNAM</t>
+  </si>
+  <si>
+    <t>RNA RESOURCES GROUP LTD.,</t>
+  </si>
+  <si>
+    <t>GROUND FLOOR, JAFZA ONE
+P.O. BOX: 17155, NEAR GATE - 12,
+JAFZA SOUTH, DUBAI, UNITED ARAB EMIRATES.
+JAFZA, DUBAI</t>
+  </si>
+  <si>
+    <t>FAM BRAND LAO</t>
+  </si>
+  <si>
+    <t>5553 BANDINI BLVD., SUITE B
+BELL GARDENS, CA, USA 90201</t>
+  </si>
+  <si>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>920</t>
   </si>
   <si>
     <t>258/KM.4/WBC.09/2024</t>
   </si>
   <si>
-    <t>12-11-2024 00:00:00</t>
-  </si>
-  <si>
-    <t>0317950343528000000000</t>
-  </si>
-  <si>
-    <t>ECO LAUNDRY HIJAU INDONESIA</t>
-  </si>
-  <si>
-    <t>JL RAYA SOLO-SRAGEN KM.20,8 RT. 28A RW. 007   KRIKILAN MASARAN KAB. SRAGEN JAWA TENGAH</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>797/TPB-SK.01/KBC.0903/2025</t>
-  </si>
-  <si>
-    <t>2025-08-27</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>147/NAG-ELH/KK/VIII/2025/003</t>
-  </si>
-  <si>
-    <t>2025-08-19</t>
-  </si>
-  <si>
-    <t>997</t>
-  </si>
-  <si>
-    <t>CBD 2025 08 898 01 41762</t>
-  </si>
-  <si>
-    <t>994</t>
-  </si>
-  <si>
-    <t>002545/BPJ/CB/2025</t>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>0535/E/NAG/0925</t>
   </si>
   <si>
     <t>217</t>
@@ -531,13 +638,28 @@
     <t>-</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>031670</t>
-  </si>
-  <si>
-    <t>2025-08-12</t>
+    <t>740</t>
+  </si>
+  <si>
+    <t>884685740426</t>
+  </si>
+  <si>
+    <t>0534/E/NAG/0925</t>
+  </si>
+  <si>
+    <t>4694138002</t>
+  </si>
+  <si>
+    <t>0515/E/NAG/0925</t>
+  </si>
+  <si>
+    <t>9740372515</t>
+  </si>
+  <si>
+    <t>0541/E/NAG/0925</t>
+  </si>
+  <si>
+    <t>4694115812</t>
   </si>
   <si>
     <t>KODE CARA ANGKUT</t>
@@ -561,6 +683,24 @@
     <t>CARA PENGANGKUTAN LAINNYA</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>5194</t>
+  </si>
+  <si>
+    <t>K - MILE AIR</t>
+  </si>
+  <si>
+    <t>8K0801</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
     <t>KODE KEMASAN</t>
   </si>
   <si>
@@ -570,7 +710,7 @@
     <t>MEREK</t>
   </si>
   <si>
-    <t>CT</t>
+    <t>PK</t>
   </si>
   <si>
     <t>NOMOR KONTINER</t>
@@ -735,22 +875,69 @@
     <t>TARIF CUKAI</t>
   </si>
   <si>
+    <t>39191020</t>
+  </si>
+  <si>
+    <t>SAMPLE ACCESORIES DUCT TAPE</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>3204</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>62014010</t>
+  </si>
+  <si>
+    <t>SM/GGF/0325/001</t>
+  </si>
+  <si>
+    <t>SAMPLE BARANG JADI 
+HOODIE/QUARTER ZIP</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>61032900</t>
+  </si>
+  <si>
+    <t>SAMPLE BARANG JADI - 
+LEG PANT/SHORT</t>
+  </si>
+  <si>
+    <t>39232199</t>
+  </si>
+  <si>
+    <t>SAMPLE (ACCESORIES)</t>
+  </si>
+  <si>
     <t>61091010</t>
   </si>
   <si>
-    <t>DIE/0825/025</t>
-  </si>
-  <si>
-    <t>GARMENT/T-SHIRT UNTUK DI WASHING</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>DIE/0825/026</t>
+    <t>GLB/CTX/0225/001</t>
+  </si>
+  <si>
+    <t>T-SHIRT 
+SAMPLE PPS WC6SK033RS</t>
+  </si>
+  <si>
+    <t>61083200</t>
+  </si>
+  <si>
+    <t>SM/RNA/0625/005</t>
+  </si>
+  <si>
+    <t>PAJAMAS
+PP SAMPLE - MAXN21970</t>
+  </si>
+  <si>
+    <t>T-SHIRT 
+PROTO SAMPLE GP012572</t>
   </si>
   <si>
     <t>KODE PUNGUTAN</t>
@@ -810,33 +997,6 @@
     <t>VALUTA</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>60064290</t>
-  </si>
-  <si>
-    <t>2771</t>
-  </si>
-  <si>
-    <t>HD62866 73% LENZING MODAL 27% VIRGIN POLYESTER 160GSM PLATED JERSEY (3747.6 YRD)</t>
-  </si>
-  <si>
-    <t>BLACK</t>
-  </si>
-  <si>
-    <t>KGM</t>
-  </si>
-  <si>
-    <t>08-12-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>00002374540620250812000195</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
   </si>
   <si>
@@ -864,16 +1024,10 @@
     <t>TANGGAL BPJ</t>
   </si>
   <si>
-    <t>08-27-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>JAMKRIDA JAKARTA</t>
-  </si>
-  <si>
-    <t>11-24-2025 00:00:00</t>
-  </si>
-  <si>
     <t>NAMA</t>
+  </si>
+  <si>
+    <t>BANK CENTRAL ASIA</t>
   </si>
   <si>
     <t>VERSI</t>
@@ -1007,7 +1161,6 @@
     <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1365,23 +1518,77 @@
       <c r="C2" t="s">
         <v>104</v>
       </c>
-      <c r="N2" t="s">
+      <c r="E2" t="s">
         <v>105</v>
       </c>
+      <c r="G2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>118</v>
+      </c>
       <c r="BK2" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN2" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO2" t="n">
-        <v>0.0</v>
+        <v>0.05</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0</v>
+        <v>2.29</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0</v>
+        <v>27.2</v>
       </c>
       <c r="BR2" t="n">
         <v>0.0</v>
@@ -1393,52 +1600,544 @@
         <v>0.0</v>
       </c>
       <c r="BU2" t="n">
-        <v>2.390701973E7</v>
+        <v>0.0</v>
       </c>
       <c r="BV2" t="n">
         <v>0.0</v>
       </c>
       <c r="BW2" t="n">
+        <v>16460.0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P3" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>108</v>
+      </c>
+      <c r="W3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>126</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>16460.0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>104</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>116</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+      <c r="P4" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>108</v>
+      </c>
+      <c r="W4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>16460.0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>104</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>136</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>116</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" t="s">
+        <v>106</v>
+      </c>
+      <c r="P5" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>108</v>
+      </c>
+      <c r="W5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>16460.0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB5" t="n">
         <v>1.0</v>
       </c>
-      <c r="BY2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>185.42</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE2" t="s">
+      <c r="CC5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>104</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>140</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>116</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA5" t="s">
         <v>106</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>108</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>109</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>110</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>111</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>107</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1469,10 +2168,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>252</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -1502,13 +2201,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1542,10 +2241,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -1557,7 +2256,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -1578,13 +2277,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="81.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1594,10 +2291,9 @@
     <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1618,64 +2314,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -1690,218 +2386,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I2" t="s">
-        <v>165</v>
-      </c>
-      <c r="J2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K2" t="s">
-        <v>165</v>
-      </c>
-      <c r="L2" t="s">
-        <v>264</v>
-      </c>
-      <c r="M2" t="n">
-        <v>88.4</v>
-      </c>
-      <c r="P2" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" t="s">
-        <v>167</v>
-      </c>
-      <c r="S2" t="s">
-        <v>265</v>
-      </c>
-      <c r="T2" t="s">
-        <v>266</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1041.1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.146084894E7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.146084894E7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H3" t="s">
-        <v>263</v>
-      </c>
-      <c r="I3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J3" t="s">
-        <v>165</v>
-      </c>
-      <c r="K3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L3" t="s">
-        <v>264</v>
-      </c>
-      <c r="M3" t="n">
-        <v>96.0</v>
-      </c>
-      <c r="P3" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>104</v>
-      </c>
-      <c r="R3" t="s">
-        <v>167</v>
-      </c>
-      <c r="S3" t="s">
-        <v>265</v>
-      </c>
-      <c r="T3" t="s">
-        <v>266</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1041.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.244617079E7</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.244617079E7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -1922,7 +2452,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1953,428 +2483,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>243</v>
+        <v>299</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I2" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1690466.39</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>264</v>
-      </c>
-      <c r="N2" t="n">
-        <v>88.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>384196.91</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M3" t="s">
-        <v>264</v>
-      </c>
-      <c r="N3" t="n">
-        <v>88.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>259</v>
-      </c>
-      <c r="E4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" t="s">
-        <v>267</v>
-      </c>
-      <c r="G4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1719127.34</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>264</v>
-      </c>
-      <c r="N4" t="n">
-        <v>88.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G5" t="n">
-        <v>24750.0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2187900.0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M5" t="s">
-        <v>264</v>
-      </c>
-      <c r="N5" t="n">
-        <v>88.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" t="s">
-        <v>105</v>
-      </c>
-      <c r="G6" t="n">
-        <v>24750.0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>116</v>
-      </c>
-      <c r="I6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2376000.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>264</v>
-      </c>
-      <c r="N6" t="n">
-        <v>96.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" t="s">
-        <v>267</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>116</v>
-      </c>
-      <c r="I7" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1866925.62</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>264</v>
-      </c>
-      <c r="N7" t="n">
-        <v>96.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" t="s">
-        <v>267</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>116</v>
-      </c>
-      <c r="I8" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1835800.61</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M8" t="s">
-        <v>264</v>
-      </c>
-      <c r="N8" t="n">
-        <v>96.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" t="s">
-        <v>267</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H9" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>417227.41</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M9" t="s">
-        <v>264</v>
-      </c>
-      <c r="N9" t="n">
-        <v>96.0</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2408,19 +2586,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>251</v>
+        <v>307</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -2441,7 +2619,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2453,72 +2631,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>801424.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3526267.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4563900.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3586052.0</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2539,16 +2661,16 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="25.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2559,57 +2681,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>269</v>
+        <v>316</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.4133E7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>278</v>
-      </c>
-      <c r="H2" t="s">
-        <v>279</v>
-      </c>
-      <c r="I2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J2" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -2630,7 +2723,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2638,13 +2732,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>280</v>
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -2667,12 +2817,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>281</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2697,12 +2847,12 @@
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="28.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="87.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="36.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="170.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2714,46 +2864,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
@@ -2761,28 +2911,28 @@
         <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I2" t="s">
-        <v>140</v>
+        <v>161</v>
+      </c>
+      <c r="H2" t="s">
+        <v>162</v>
       </c>
       <c r="J2" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
@@ -2790,37 +2940,22 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="G3" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" t="s">
-        <v>144</v>
-      </c>
-      <c r="I3" t="s">
-        <v>140</v>
-      </c>
-      <c r="J3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K3" t="s">
-        <v>145</v>
-      </c>
-      <c r="L3" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4">
@@ -2828,28 +2963,487 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="F4" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="G4" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I4" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>172</v>
+      </c>
+      <c r="O4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" t="s">
+        <v>174</v>
+      </c>
+      <c r="M5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" t="s">
+        <v>174</v>
+      </c>
+      <c r="M7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" t="s">
+        <v>161</v>
+      </c>
+      <c r="H8" t="s">
+        <v>162</v>
+      </c>
+      <c r="J8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" t="s">
+        <v>179</v>
+      </c>
+      <c r="I9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J9" t="s">
+        <v>172</v>
+      </c>
+      <c r="O9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" t="s">
+        <v>181</v>
+      </c>
+      <c r="M10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" t="s">
+        <v>181</v>
+      </c>
+      <c r="M12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G15" t="s">
+        <v>179</v>
+      </c>
+      <c r="I15" t="s">
+        <v>171</v>
+      </c>
+      <c r="J15" t="s">
+        <v>172</v>
+      </c>
+      <c r="O15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" t="s">
+        <v>182</v>
+      </c>
+      <c r="G16" t="s">
+        <v>183</v>
+      </c>
+      <c r="M16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" t="s">
+        <v>176</v>
+      </c>
+      <c r="F18" t="s">
+        <v>182</v>
+      </c>
+      <c r="G18" t="s">
+        <v>183</v>
+      </c>
+      <c r="M18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" t="s">
+        <v>161</v>
+      </c>
+      <c r="H20" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21" t="s">
+        <v>178</v>
+      </c>
+      <c r="G21" t="s">
+        <v>179</v>
+      </c>
+      <c r="I21" t="s">
+        <v>171</v>
+      </c>
+      <c r="J21" t="s">
+        <v>172</v>
+      </c>
+      <c r="O21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" t="s">
+        <v>185</v>
+      </c>
+      <c r="M22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" t="s">
+        <v>176</v>
+      </c>
+      <c r="F24" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" t="s">
+        <v>185</v>
+      </c>
+      <c r="M24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2872,7 +3466,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="29.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2883,22 +3477,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2">
@@ -2909,13 +3503,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3">
@@ -2926,13 +3520,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -2943,13 +3537,13 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -2960,47 +3554,217 @@
         <v>4.0</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B6" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B7" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E7" t="s">
-        <v>168</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D10" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>193</v>
+      </c>
+      <c r="D15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>195</v>
+      </c>
+      <c r="D16" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3036,28 +3800,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2">
@@ -3068,7 +3832,76 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>212</v>
+      </c>
+      <c r="D2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3099,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
@@ -3119,10 +3952,64 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3155,19 +4042,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3191,8 +4078,8 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="33.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="39.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3207,8 +4094,7 @@
     <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="34" max="34" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3252,58 +4138,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -3315,19 +4201,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -3342,25 +4228,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -3369,82 +4255,82 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>216</v>
+        <v>258</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>220</v>
+        <v>262</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>221</v>
+        <v>263</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
@@ -3455,55 +4341,55 @@
         <v>102</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="F2" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="G2" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="H2" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="I2" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="J2" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="K2" t="n">
-        <v>480.0</v>
+        <v>1.0</v>
       </c>
       <c r="L2" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="M2" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="T2" t="n">
-        <v>96.0</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.244617079E7</v>
+        <v>0.0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.244617079E7</v>
+        <v>0.0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.0</v>
+        <v>16426.0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0</v>
+        <v>0.1</v>
       </c>
       <c r="AF2" t="n">
         <v>0.0</v>
@@ -3517,6 +4403,9 @@
       <c r="AI2" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AK2" t="n">
         <v>0.0</v>
       </c>
@@ -3526,14 +4415,17 @@
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR2" t="s">
-        <v>142</v>
+      <c r="AS2" t="s">
+        <v>279</v>
       </c>
       <c r="AY2" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -3541,85 +4433,560 @@
         <v>102</v>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16426.0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>279</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>280</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F3" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K3" t="n">
-        <v>442.0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>179</v>
-      </c>
-      <c r="M3" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>88.4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.146084894E7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.146084894E7</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="C4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I4" t="s">
+        <v>196</v>
+      </c>
+      <c r="J4" t="s">
+        <v>284</v>
+      </c>
+      <c r="K4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>221</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16426.0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>142</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>238</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.0</v>
+      <c r="AK4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>279</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>280</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J5" t="s">
+        <v>284</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>221</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>16426.0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>279</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>280</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16460.0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>279</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>280</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" t="s">
+        <v>196</v>
+      </c>
+      <c r="H7" t="s">
+        <v>196</v>
+      </c>
+      <c r="I7" t="s">
+        <v>196</v>
+      </c>
+      <c r="J7" t="s">
+        <v>284</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16460.0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>280</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F8" t="s">
+        <v>196</v>
+      </c>
+      <c r="G8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" t="s">
+        <v>196</v>
+      </c>
+      <c r="I8" t="s">
+        <v>196</v>
+      </c>
+      <c r="J8" t="s">
+        <v>284</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>221</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16460.0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>279</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>280</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3665,58 +5032,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>243</v>
+        <v>299</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3737,7 +5104,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3748,35 +5115,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>307</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
